--- a/Processed_Data/PM25_check.xlsx
+++ b/Processed_Data/PM25_check.xlsx
@@ -1435,7 +1435,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2635,7 +2635,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3835,7 +3835,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5035,7 +5035,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6235,7 +6235,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -7435,7 +7435,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -8635,7 +8635,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -9835,7 +9835,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="B393" t="n">

--- a/Processed_Data/PM25_check.xlsx
+++ b/Processed_Data/PM25_check.xlsx
@@ -1435,7 +1435,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2635,7 +2635,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3835,7 +3835,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5035,7 +5035,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6235,7 +6235,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -7435,7 +7435,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -8635,7 +8635,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -9835,7 +9835,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B393" t="n">
